--- a/output/pdf_financials_xlsx/VER.H.xlsx
+++ b/output/pdf_financials_xlsx/VER.H.xlsx
@@ -15508,10 +15508,10 @@
         </is>
       </c>
       <c r="J174" s="5" t="n">
-        <v>1.201589</v>
+        <v>-1.201589</v>
       </c>
       <c r="K174" s="5" t="n">
-        <v>1.201589</v>
+        <v>-1.201589</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/VER.H.xlsx
+++ b/output/pdf_financials_xlsx/VER.H.xlsx
@@ -721,31 +721,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.045566</v>
+        <v>3.497623</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.108228</v>
+        <v>2.48305</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.005391</v>
+        <v>1.543059</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>0.15936</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>0.192252</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>0.28799</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>0.136269</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>0.114767</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>0.11576</v>
       </c>
     </row>
     <row r="11">
@@ -1592,31 +1592,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.339611</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.011416</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.137477</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.085781</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.030425</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.007596</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.000743</v>
       </c>
     </row>
     <row r="35">
@@ -1660,31 +1660,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.339611</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.011416</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.137477</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.085781</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.030425</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.007596</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.000743</v>
       </c>
     </row>
     <row r="37">
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.655917</v>
+        <v>0.316306</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.245753</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.243556</v>
+        <v>0.23214</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">

--- a/output/pdf_financials_xlsx/VER.H.xlsx
+++ b/output/pdf_financials_xlsx/VER.H.xlsx
@@ -2654,31 +2654,31 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.770732</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.945404</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.283991</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.04345</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.04345</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.000663</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.002193</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.003981</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.002333</v>
       </c>
     </row>
     <row r="65">
